--- a/lod_precision_profile/template_lod_precision_profile.xlsx
+++ b/lod_precision_profile/template_lod_precision_profile.xlsx
@@ -357,6 +357,9 @@
   </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.5"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
